--- a/output/pdf_financials_xlsx/CRTL.xlsx
+++ b/output/pdf_financials_xlsx/CRTL.xlsx
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.018651</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.041513</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>11.58939</v>
       </c>
     </row>
     <row r="35">
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.003</v>
+        <v>0.021651</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.003125</v>
+        <v>0.044638</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.779546</v>
+        <v>12.368936</v>
       </c>
     </row>
     <row r="37">
@@ -1400,13 +1400,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.031162</v>
+        <v>0.012511</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.097735</v>
+        <v>0.056222</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>11.643525</v>
+        <v>0.054135</v>
       </c>
     </row>
     <row r="49">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/CRTL.xlsx
+++ b/output/pdf_financials_xlsx/CRTL.xlsx
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.687057</v>
+        <v>0.787532</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.977838</v>
+        <v>2.1542</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1.098704</v>
+        <v>1.191433</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1.187181</v>
+        <v>1.390097</v>
       </c>
     </row>
     <row r="8">
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.687057</v>
+        <v>0.787532</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.977838</v>
+        <v>2.1542</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.098704</v>
+        <v>1.191433</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.187181</v>
+        <v>1.390097</v>
       </c>
     </row>
     <row r="11">
@@ -1100,10 +1100,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.678516</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.018651</v>
@@ -1121,10 +1119,8 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0.0105</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0.003</v>
@@ -1142,10 +1138,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.689016</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.021651</v>
@@ -1163,10 +1157,8 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0.119337</v>
       </c>
       <c r="C37" s="3" t="n">
         <v>0.264141</v>
@@ -1184,10 +1176,8 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
         <v>0</v>
@@ -1205,10 +1195,8 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
         <v>0</v>
@@ -1226,10 +1214,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0</v>
@@ -1247,10 +1233,8 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.119337</v>
       </c>
       <c r="C41" s="3" t="n">
         <v>0.264141</v>
@@ -1268,10 +1252,8 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
         <v>0</v>
@@ -1289,10 +1271,8 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
         <v>0</v>
@@ -1310,10 +1290,8 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
         <v>0</v>
@@ -1331,10 +1309,8 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
         <v>0</v>
@@ -1352,10 +1328,8 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
         <v>0</v>
@@ -1373,10 +1347,8 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
         <v>0</v>
@@ -1394,10 +1366,8 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.186897</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.012511</v>
@@ -1415,10 +1385,8 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>0.99525</v>
       </c>
       <c r="C49" s="3" t="n">
         <v>0.298303</v>
@@ -1436,10 +1404,8 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="3" t="n">
         <v>0</v>
@@ -1457,10 +1423,8 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
         <v>0</v>
@@ -1478,10 +1442,8 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C52" s="3" t="n">
         <v>0</v>
@@ -1499,10 +1461,8 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0.008512</v>
       </c>
       <c r="C53" s="3" t="n">
         <v>0.006808</v>
@@ -1520,10 +1480,8 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C54" s="3" t="n">
         <v>0</v>
@@ -1568,10 +1526,8 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>0</v>
@@ -1589,10 +1545,8 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>0</v>
@@ -1610,10 +1564,8 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>2.675288</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>2.095511</v>
@@ -1631,10 +1583,8 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>0</v>
@@ -1652,10 +1602,8 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>0</v>
@@ -1673,10 +1621,8 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.008512</v>
       </c>
       <c r="C61" s="3" t="n">
         <v>0.006808</v>
@@ -1694,10 +1640,8 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>2.6838</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>2.102319</v>
@@ -1715,10 +1659,8 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>3.67905</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>2.400622</v>
@@ -1736,10 +1678,8 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>0</v>
@@ -1757,10 +1697,8 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C65" s="3" t="n">
         <v>0</v>
@@ -1778,10 +1716,8 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C66" s="3" t="n">
         <v>0</v>
@@ -1799,10 +1735,8 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>0</v>
@@ -1820,10 +1754,8 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.042237</v>
       </c>
       <c r="C68" s="3" t="n">
         <v>0.532377</v>
@@ -1841,10 +1773,8 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C69" s="3" t="n">
         <v>0</v>
@@ -1862,10 +1792,8 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>0</v>
@@ -1883,10 +1811,8 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
         <v>0</v>
@@ -1904,10 +1830,8 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C72" s="3" t="n">
         <v>0.040746</v>
@@ -1925,10 +1849,8 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C73" s="3" t="n">
         <v>0</v>
@@ -1946,10 +1868,8 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C74" s="3" t="n">
         <v>0.040746</v>
@@ -1967,10 +1887,8 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
         <v>0</v>
@@ -2015,10 +1933,8 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>0</v>
@@ -2036,10 +1952,8 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>0</v>
@@ -2057,10 +1971,8 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>0</v>
@@ -2105,10 +2017,8 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>0</v>
@@ -2126,10 +2036,8 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C82" s="3" t="n">
         <v>0</v>
@@ -2147,10 +2055,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C83" s="3" t="n">
         <v>0</v>
@@ -2168,10 +2074,8 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C84" s="3" t="n">
         <v>0</v>
@@ -2189,10 +2093,8 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
         <v>0</v>
@@ -2237,10 +2139,8 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>0.042237</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>0.573123</v>
@@ -2258,10 +2158,8 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>8.227098</v>
       </c>
       <c r="C88" s="3" t="n">
         <v>10.963571</v>
@@ -2279,10 +2177,8 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>0</v>
@@ -2300,10 +2196,8 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-5.903646</v>
       </c>
       <c r="C90" s="3" t="n">
         <v>-10.708116</v>
@@ -2321,10 +2215,8 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C91" s="3" t="n">
         <v>0</v>
@@ -2342,10 +2234,8 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0.9051709999999999</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>1.443988</v>
@@ -2363,10 +2253,8 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>0</v>
@@ -2384,10 +2272,8 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>3.636813</v>
       </c>
       <c r="C94" s="3" t="n">
         <v>1.827499</v>
@@ -2405,10 +2291,8 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C95" s="3" t="n">
         <v>0</v>
@@ -2426,10 +2310,8 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>3.636813</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>1.827499</v>
@@ -2447,10 +2329,8 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.9885195906551963</v>
       </c>
       <c r="C97" s="3" t="n">
         <v>0.7612606232884644</v>
@@ -2704,7 +2584,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00375</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2789,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="116">
@@ -3149,7 +3029,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00375</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -3168,7 +3048,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.414092</v>
+        <v>-1.417842</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-1.076538</v>
@@ -3191,7 +3071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3263,10 +3143,8 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" s="5" t="n">
+        <v>0.678516</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>0.018651</v>
@@ -3371,10 +3249,8 @@
           <t>PrepaidAssets</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E5" s="5" t="n">
+        <v>0.186897</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.012511</v>
@@ -3407,10 +3283,8 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>0.99525</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.298303</v>
@@ -3443,10 +3317,8 @@
           <t>MachineryFurnitureEquipment</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>0.008512</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.006808</v>
@@ -3515,10 +3387,8 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="5" t="n">
+        <v>3.67905</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>2.400622</v>
@@ -3592,10 +3462,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="5" t="n">
+        <v>0.040746</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0.203145</v>
@@ -3625,10 +3493,8 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E12" s="5" t="n">
+        <v>0.042237</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0.573123</v>
@@ -3749,10 +3615,8 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E16" s="5" t="n">
+        <v>-5.903646</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>-10.708116</v>
@@ -3781,10 +3645,8 @@
           <t>TotalEquityGrossMinorityInterest</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E17" s="5" t="n">
+        <v>3.636813</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>1.827499</v>
@@ -3813,10 +3675,8 @@
           <t>TotalEquityGrossMinorityInterest</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E18" s="5" t="n">
+        <v>3.67905</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>2.400622</v>
@@ -3869,239 +3729,251 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Marketable securities (note 4)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ShortTermInvestments</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-2.127108</v>
+        <v>0.0105</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-4.80447</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>-1.682881</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-2.809805</v>
+        <v>0.003</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Current assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Amounts receivable (note 5)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>AccountsReceivable</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.002363</v>
+        <v>0.119337</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.001704</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.001364</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>0.001088</v>
+        <v>0.264141</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Non-current assets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Exploration and evaluation assets (note 6)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>NetPPE</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.944921</v>
+        <v>2.675288</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.458352</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.342549</v>
-      </c>
-      <c r="H22" s="5" t="n">
-        <v>1.171836</v>
+        <v>2.095511</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities (note 10) $</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.042237</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.532377</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H23" s="5" t="n">
-        <v>-0.066523</v>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Share capital (note 7)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>0.0285</v>
+        <v>8.227098</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.001125</v>
-      </c>
-      <c r="H24" s="5" t="n">
-        <v>0.110746</v>
+        <v>10.963571</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities</t>
+          <t>Warrants (note 8)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="5" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.128056</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>-0.008449999999999999</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Adjustments for</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shares issued for services</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Contributed surplus (note 9)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.9051709999999999</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.89925</v>
+        <v>1.443988</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H26" s="5" t="n">
-        <v>0.0495</v>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -4112,30 +3984,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Net loss for the year $</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-0.099312</v>
+        <v>-2.127108</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.144804</v>
+        <v>-4.80447</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.220208</v>
+        <v>-1.682881</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.010731</v>
+        <v>-2.809805</v>
       </c>
     </row>
     <row r="28">
@@ -4146,30 +4018,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-0.175032</v>
+        <v>0.002363</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.174386</v>
+        <v>0.001704</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.043711</v>
+        <v>0.001364</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.002087</v>
+        <v>0.001088</v>
       </c>
     </row>
     <row r="29">
@@ -4180,30 +4052,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.011576</v>
+        <v>0.944921</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.49014</v>
+        <v>0.458352</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.22691</v>
+        <v>0.342549</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.219272</v>
+        <v>1.171836</v>
       </c>
     </row>
     <row r="30">
@@ -4214,32 +4086,32 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" s="5" t="n">
-        <v>0.040746</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.162399</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-0.000449</v>
+        <v>-0.066523</v>
       </c>
     </row>
     <row r="31">
@@ -4250,30 +4122,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Unrealized loss on fair value of marketable securities</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" s="5" t="n">
-        <v>-1.414092</v>
+        <v>0.0285</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>-1.076538</v>
+        <v>0.0075</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.772037</v>
+        <v>0.001125</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>-1.319967</v>
+        <v>0.110746</v>
       </c>
     </row>
     <row r="32">
@@ -4284,12 +4152,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Proceeds from sale of marketable securities</t>
+          <t>Realized gain on sale of marketable securities</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -4309,7 +4177,7 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.0097</v>
+        <v>-0.008449999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -4320,26 +4188,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Exploration activities and maintenance of properties</t>
+          <t>Shares issued for services</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" s="5" t="n">
-        <v>-0.189638</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.854881</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>-0.756698</v>
+        <v>0.89925</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>-0.984951</v>
+        <v>0.0495</v>
       </c>
     </row>
     <row r="34">
@@ -4350,34 +4222,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Recovery from exploration and evaluation assets</t>
+          <t>Amounts receivable</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>-0.099312</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.144804</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.220208</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.121691</v>
+        <v>0.010731</v>
       </c>
     </row>
     <row r="35">
@@ -4388,30 +4256,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.193388</v>
+        <v>-0.175032</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.804881</v>
+        <v>0.174386</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.756698</v>
+        <v>-0.043711</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-0.85356</v>
+        <v>0.002087</v>
       </c>
     </row>
     <row r="36">
@@ -4422,28 +4290,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Issuance of units for cash</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.959398</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011576</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.49014</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1.664729</v>
+        <v>0.22691</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>13.166199</v>
+        <v>0.219272</v>
       </c>
     </row>
     <row r="37">
@@ -4454,32 +4324,32 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Deferred revenue</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>-0.052243</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.040746</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.113132</v>
+        <v>0.162399</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>-0.937658</v>
+        <v>-0.000449</v>
       </c>
     </row>
     <row r="38">
@@ -4490,32 +4360,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stock options exercised</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-1.414092</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-1.076538</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-0.772037</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.28665</v>
+        <v>-1.319967</v>
       </c>
     </row>
     <row r="39">
@@ -4526,20 +4394,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Warrants exercised</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>0.1197</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1.221554</v>
+          <t>Proceeds from sale of marketable securities</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4547,7 +4423,7 @@
         </is>
       </c>
       <c r="H39" s="5" t="n">
-        <v>1.206213</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="40">
@@ -4558,30 +4434,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Exploration activities and maintenance of properties</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>1.026855</v>
+        <v>-0.189638</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>1.221554</v>
+        <v>-0.854881</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1.551597</v>
+        <v>-0.756698</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>13.721404</v>
+        <v>-0.984951</v>
       </c>
     </row>
     <row r="41">
@@ -4592,30 +4464,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
+          <t>Recovery from exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="n">
-        <v>-0.5806249999999999</v>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.659865</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.022862</v>
+        <v>0.05</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H41" s="5" t="n">
-        <v>11.547877</v>
+        <v>0.121691</v>
       </c>
     </row>
     <row r="42">
@@ -4626,30 +4502,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1.259141</v>
+        <v>-0.193388</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.678516</v>
+        <v>-0.804881</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.018651</v>
+        <v>-0.756698</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.041513</v>
+        <v>-0.85356</v>
       </c>
     </row>
     <row r="43">
@@ -4665,25 +4541,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Issuance of units for cash</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>0.678516</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.018651</v>
+        <v>0.959398</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.041513</v>
+        <v>1.664729</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>11.58939</v>
+        <v>13.166199</v>
       </c>
     </row>
     <row r="44">
@@ -4694,19 +4568,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shares and units issued for debt settlement $</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-0.052243</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4714,10 +4590,10 @@
         </is>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.210631</v>
+        <v>-0.113132</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.182937</v>
+        <v>-0.937658</v>
       </c>
     </row>
     <row r="45">
@@ -4728,20 +4604,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shares issued for property acquisition $</t>
+          <t>Stock options exercised</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>2.295166</v>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>0.416</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4749,7 +4629,7 @@
         </is>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.5165</v>
+        <v>0.28665</v>
       </c>
     </row>
     <row r="46">
@@ -4760,30 +4640,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Finders' warrants $</t>
+          <t>Warrants exercised</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="n">
-        <v>0.021463</v>
+      <c r="E46" s="5" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>1.221554</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.282703</v>
+        <v>1.206213</v>
       </c>
     </row>
     <row r="47">
@@ -4794,36 +4672,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adjustments for</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and evaluation assets</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>1.026855</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>1.800658</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.221554</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1.551597</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>13.721404</v>
       </c>
     </row>
     <row r="48">
@@ -4834,32 +4706,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Units issued for debt settlement $</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>-0.5806249999999999</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>-0.659865</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.210631</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.022862</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>11.547877</v>
       </c>
     </row>
     <row r="49">
@@ -4870,270 +4740,280 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Purchase of equipment</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
-        <v>-0.00375</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.259141</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.678516</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.018651</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.041513</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Professional fees (note 9) $</t>
+          <t>Cash, end of year $</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.678516</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.152247</v>
+        <v>0.018651</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.094319</v>
+        <v>0.041513</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.170516</v>
+        <v>11.58939</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Consulting fees (notes 6 and 9)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Shares and units issued for debt settlement $</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" s="5" t="n">
-        <v>1.369302</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.596119</v>
+        <v>0.210631</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.523925</v>
+        <v>0.182937</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>General office expenses</t>
+          <t>Shares issued for property acquisition $</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.100475</v>
+        <v>2.295166</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.176362</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.09272900000000001</v>
+        <v>0.416</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.202916</v>
+        <v>0.5165</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.317937</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.589967</v>
+          <t>Finders' warrants $</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.487732</v>
+        <v>0.021463</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.634416</v>
+        <v>0.282703</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Adjustments for</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Shareholder information and communication</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.057144</v>
+          <t>Impairment loss on exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.06139</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.042209</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0.047684</v>
+        <v>1.800658</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="n">
-        <v>0.016346</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>0.018569</v>
+          <t>Units issued for debt settlement $</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.014853</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>0.02884</v>
+        <v>0.210631</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
+          <t>Purchase of equipment</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.00375</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n">
-        <v>0.009882</v>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>-0.007189</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -5149,25 +5029,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Professional fees (note 9) $</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>0.002363</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.001704</v>
+        <v>0.152247</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.001364</v>
+        <v>0.094319</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.001088</v>
+        <v>0.170516</v>
       </c>
     </row>
     <row r="58">
@@ -5183,23 +5065,27 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Share-based payments (notes 8 and 9)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Consulting fees (notes 6 and 9)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.458352</v>
+        <v>1.369302</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.342549</v>
+        <v>0.596119</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>1.171836</v>
+        <v>0.523925</v>
       </c>
     </row>
     <row r="59">
@@ -5215,25 +5101,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
+          <t>General office expenses</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>-2.098608</v>
+        <v>0.100475</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-2.996312</v>
+        <v>0.176362</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-1.681756</v>
+        <v>0.09272900000000001</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>-2.774032</v>
+        <v>0.202916</v>
       </c>
     </row>
     <row r="60">
@@ -5244,30 +5130,30 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of marketable securities (note 3)</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0.317937</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0.589967</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.001125</v>
+        <v>0.487732</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>-0.110746</v>
+        <v>0.634416</v>
       </c>
     </row>
     <row r="61">
@@ -5278,32 +5164,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (note 6)</t>
+          <t>Shareholder information and communication</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E61" s="5" t="n">
+        <v>0.057144</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>0.06139</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.042209</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.066523</v>
+        <v>0.047684</v>
       </c>
     </row>
     <row r="62">
@@ -5314,32 +5194,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Realized gain on sale of marketable securities (note 3)</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0.016346</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0.018569</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.014853</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.008449999999999999</v>
+        <v>0.02884</v>
       </c>
     </row>
     <row r="63">
@@ -5350,17 +5228,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5374,10 +5252,10 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-1.682881</v>
+        <v>0.009882</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>-2.809805</v>
+        <v>-0.007189</v>
       </c>
     </row>
     <row r="64">
@@ -5388,30 +5266,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share $</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="n">
+        <v>0.002363</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.001704</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.001364</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.001088</v>
       </c>
     </row>
     <row r="65">
@@ -5422,12 +5300,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Unrealized gain (loss) on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+          <t>Share-based payments (notes 8 and 9)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5436,16 +5314,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F65" s="5" t="n">
+        <v>0.458352</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>30.462358</v>
+        <v>0.342549</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>42.165804</v>
+        <v>1.171836</v>
       </c>
     </row>
     <row r="66">
@@ -5461,25 +5337,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
-        <v>0.14412</v>
+        <v>-2.098608</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.171736</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.996312</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-1.681756</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>-2.774032</v>
       </c>
     </row>
     <row r="67">
@@ -5490,34 +5366,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Unrealized gain (loss) on fair value of</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Unrealized gain (loss) on fair value of marketable securities (note 3)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F67" s="5" t="n">
-        <v>-0.003317</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.009882</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001125</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>-0.110746</v>
       </c>
     </row>
     <row r="68">
@@ -5528,12 +5400,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of</t>
+          <t>Unrealized gain (loss) on fair value of</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities (note 3)</t>
+          <t>Gain on debt settlement (note 6)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -5542,16 +5414,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>-0.001125</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>0.066523</v>
       </c>
     </row>
     <row r="69">
@@ -5562,12 +5436,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and</t>
+          <t>Unrealized gain (loss) on fair value of</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and evaluation assets (note 5)</t>
+          <t>Realized gain on sale of marketable securities (note 3)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5576,18 +5450,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>-1.800658</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H69" s="5" t="n">
+        <v>0.008449999999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5598,7 +5472,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and</t>
+          <t>Unrealized gain (loss) on fair value of</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5616,16 +5490,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" s="5" t="n">
-        <v>-4.80447</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G70" s="5" t="n">
         <v>-1.682881</v>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H70" s="5" t="n">
+        <v>-2.809805</v>
       </c>
     </row>
     <row r="71">
@@ -5636,7 +5510,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and</t>
+          <t>Unrealized gain (loss) on fair value of</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5650,16 +5524,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="5" t="n">
-        <v>-2e-07</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G71" s="5" t="n">
         <v>-5.999999999999999e-08</v>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H71" s="5" t="n">
+        <v>-7e-08</v>
       </c>
     </row>
     <row r="72">
@@ -5670,7 +5544,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and</t>
+          <t>Unrealized gain (loss) on fair value of</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5684,16 +5558,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>24.424629</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G72" s="5" t="n">
         <v>30.462358</v>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H72" s="5" t="n">
+        <v>42.165804</v>
       </c>
     </row>
     <row r="73">
@@ -5709,19 +5583,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Professional fees (note 10) $</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>0.193373</v>
+        <v>0.14412</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.152247</v>
+        <v>0.171736</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5747,24 +5617,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Consulting fees (notes 7 and 10)</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>0.352774</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>1.369302</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.003317</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.009882</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5780,29 +5650,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Unrealized loss on fair value of</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>-0.030845</v>
+          <t>Unrealized loss on fair value of marketable securities (note 3)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.003317</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0075</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>-0.001125</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5818,20 +5684,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Impairment loss on exploration and</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Share-based payments (notes 9 and 10)</t>
+          <t>Impairment loss on exploration and evaluation assets (note 5)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>0.944921</v>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.458352</v>
+        <v>-1.800658</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5852,25 +5720,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of</t>
+          <t>Impairment loss on exploration and</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of marketable securities (note 4)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>-0.0285</v>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.0075</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.80447</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>-1.682881</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5886,12 +5758,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of</t>
+          <t>Impairment loss on exploration and</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Impairment loss on exploration and evaluation assets (note 6)</t>
+          <t>Basic and diluted net loss per share $</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -5901,12 +5773,10 @@
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-1.800658</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-07</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5922,29 +5792,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of</t>
+          <t>Impairment loss on exploration and</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="n">
-        <v>-2.127108</v>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>-4.80447</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>24.424629</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>30.462358</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5960,20 +5826,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Unrealized loss on fair value of</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Basic and diluted net loss per share $</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Professional fees (note 10) $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
-        <v>-1.2e-07</v>
+        <v>0.193373</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>-2e-07</v>
+        <v>0.152247</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5994,27 +5864,279 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Consulting fees (notes 7 and 10)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>0.352774</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>1.369302</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>-0.030845</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-0.003317</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Share-based payments (notes 9 and 10)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>0.944921</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.458352</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Unrealized loss on fair value of</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Unrealized loss on fair value of marketable securities (note 4)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>-0.0285</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Unrealized loss on fair value of</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Impairment loss on exploration and evaluation assets (note 6)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-1.800658</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Unrealized loss on fair value of</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>-2.127108</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-4.80447</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Unrealized loss on fair value of</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Basic and diluted net loss per share $</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>-1.2e-07</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-2e-07</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Unrealized loss on fair value of</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding - basic and diluted</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
         <v>17.108793</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F88" s="5" t="n">
         <v>24.424629</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>-</t>
         </is>
